--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/نظم المعلومات الإدارية_طالبات.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/نظم المعلومات الإدارية_طالبات.xlsx
@@ -521,7 +521,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="str">
-        <v>منى ماجد محمد اليامي</v>
+        <v>إيمان سفر عباد المطيري</v>
       </c>
       <c r="C7" t="str">
         <v>324</v>
@@ -541,7 +541,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>أريج محمد حسن عبدالغني العوفي</v>
+        <v>سعاد عبدالله صالح المالكي</v>
       </c>
       <c r="C8" t="str">
         <v>325</v>
@@ -581,7 +581,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="str">
-        <v>أريج محمد حسن عبدالغني العوفي</v>
+        <v>نوف محمد سعد الظاهري</v>
       </c>
       <c r="C10" t="str">
         <v>325</v>
@@ -601,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="str">
-        <v>نوره علي احمد السفياني</v>
+        <v>هناء علي ظافر القرني</v>
       </c>
       <c r="C11" t="str">
         <v>323</v>
@@ -621,7 +621,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="str">
-        <v>نوره علي احمد السفياني</v>
+        <v>دلال مفرح علي العمري</v>
       </c>
       <c r="C12" t="str">
         <v>323</v>
@@ -641,7 +641,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="str">
-        <v>اماني مصطفي يوسف غزاوي</v>
+        <v>لطيفه سعد عبد الله الزهراني</v>
       </c>
       <c r="C13" t="str">
         <v>326</v>
@@ -661,7 +661,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="str">
-        <v>اماني مصطفي يوسف غزاوي</v>
+        <v>لمياء سعد أحمد الحازمي</v>
       </c>
       <c r="C14" t="str">
         <v>326</v>
@@ -701,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="str">
-        <v>منى ماجد محمد اليامي</v>
+        <v>نجود محمد جويعد الحجي السفياني</v>
       </c>
       <c r="C16" t="str">
         <v>324</v>
